--- a/marketing_report/outputs/Posgrados/Analisis_CRM/16_Falsos_Positivos_CRM.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_CRM/16_Falsos_Positivos_CRM.xlsx
@@ -425,20 +425,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA1"/>
+  <dimension ref="A1:CF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Consulta: ID Consulta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Id. candidato/contacto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Consulta: ID Consulta</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Correo</t>
@@ -456,373 +456,628 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Carrera</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Modo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Código Carrera</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Carrera</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CódigoSede</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Sede Nombre</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>FuenteLead</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>UtmSource</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>UtmCampaign</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>UtmMedium</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>UtmTerm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>UtmContent</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ColaNombre</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Gestionados</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Consulta: Fecha de creación</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Grado de Consulta</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de última interacción</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Consulta: Creado por</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Carrera</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Modo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Código Carrera</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Carrera</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>CódigoSede</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Sede Nombre</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FuenteLead</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>UtmSource</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>UtmCampaign</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>UtmMedium</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>UtmTerm</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>UtmContent</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ColaNombre</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Consulta: Fecha de creación</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>PrimeraCola</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Consulta: Nombre del propietario</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Matriculadas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Cod. Lugar</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Lugar</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Cod. Sector</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Cod. Carrera</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Cod. Modo</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Tipcar</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Tipo de DNI</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Apellido y Nombre</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Celular</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Cod. Operador</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Cod. Empresa</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Cod. Vendedor</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Haber</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Tipo Origen</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Fecha Aplicación</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Anio Aplicación</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Conceptos</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Reci. - Trans.</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Lugar</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Insc_Lugar</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Sector</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Insc_Sector</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Carrera</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Insc_Carrera</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Modo</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Insc_Modo</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Insc_Tipcar</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Insc_Tipo de DNI</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Insc_DNI</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Insc_Apellido y Nombre</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Insc_Email</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Insc_Telefono</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Insc_Celular</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Operador</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Empresa</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Insc_Empresa</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Insc_Cod. Vendedor</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Insc_Vendedor</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Insc_Fecha Pago</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Insc_Haber</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Insc_Tipo Origen</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Insc_Fecha Aplicación</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Insc_Anio Aplicación</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>Insc_Conceptos</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Insc_Reci. - Trans.</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Insc_Apellido</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Insc_Nombres</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>Match_Tipo</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>Matriculadas_Num</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1597830</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>andreabellido@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Andrea Viviana</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>24790890</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>543884440067</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Grado</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Distancia</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>355</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ESCRIBANÍA</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DELEGACION S S DE JUJUY - JUJUY</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Solicitud creada</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Camila Lamas Cil</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>SALTA - DISTANCIA</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>VICERRECTORADO ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>352</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DOCENCIA UNIVERSITARIA</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>CAMPUS VIRTUAL</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Postgrado</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>DNI-LE-LC</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>24790890</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>BELLIDO LEON, ANDREA VIVIANA</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>andreabellido@hotmail.com</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>388 - 4440067</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>388 - 4440067</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>101</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>SUB SEDE JUJUY</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>CAMILA LAMAS CIL</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="BW2" t="n">
+        <v>159950</v>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>PORTAL VENTAS</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>BELLIDO LEON</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>ANDREA VIVIANA</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>Exacto (DNI)</t>
+        </is>
+      </c>
+      <c r="CF2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Posgrados/Analisis_CRM/16_Falsos_Positivos_CRM.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_CRM/16_Falsos_Positivos_CRM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="137">
   <si>
     <t>Consulta: ID Consulta</t>
   </si>
@@ -265,6 +265,84 @@
     <t>Match_Tipo</t>
   </si>
   <si>
+    <t>Bol_Cod. Lugar</t>
+  </si>
+  <si>
+    <t>Bol_Lugar</t>
+  </si>
+  <si>
+    <t>Bol_Cod. Sector</t>
+  </si>
+  <si>
+    <t>Bol_Sector</t>
+  </si>
+  <si>
+    <t>Bol_Cod. Carrera</t>
+  </si>
+  <si>
+    <t>Bol_Carrera</t>
+  </si>
+  <si>
+    <t>Bol_Cod. Modo</t>
+  </si>
+  <si>
+    <t>Bol_Modo</t>
+  </si>
+  <si>
+    <t>Bol_Tipcar</t>
+  </si>
+  <si>
+    <t>Bol_Tipo de DNI</t>
+  </si>
+  <si>
+    <t>Bol_DNI</t>
+  </si>
+  <si>
+    <t>Bol_Apellido y Nombre</t>
+  </si>
+  <si>
+    <t>Bol_Email</t>
+  </si>
+  <si>
+    <t>Bol_Telefono</t>
+  </si>
+  <si>
+    <t>Bol_Celular</t>
+  </si>
+  <si>
+    <t>Bol_Fecha</t>
+  </si>
+  <si>
+    <t>Bol_Nro Transac</t>
+  </si>
+  <si>
+    <t>Bol_Nro Comp1</t>
+  </si>
+  <si>
+    <t>Bol_Nro Comp2</t>
+  </si>
+  <si>
+    <t>Bol_Concepto</t>
+  </si>
+  <si>
+    <t>Bol_Cod. Vendedor</t>
+  </si>
+  <si>
+    <t>Bol_Vendedor</t>
+  </si>
+  <si>
+    <t>Bol_Apellido</t>
+  </si>
+  <si>
+    <t>Bol_Nombres</t>
+  </si>
+  <si>
+    <t>Bol_Match_Tipo</t>
+  </si>
+  <si>
+    <t>Campana_Lead</t>
+  </si>
+  <si>
     <t>Matriculadas_Num</t>
   </si>
   <si>
@@ -344,6 +422,9 @@
   </si>
   <si>
     <t>Exacto (DNI)</t>
+  </si>
+  <si>
+    <t>Campaña Anterior</t>
   </si>
 </sst>
 </file>
@@ -701,10 +782,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CF2"/>
+  <dimension ref="A1:DF2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:84">
+    <row r="1" spans="1:110">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,49 +1038,127 @@
       <c r="CF1" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="CG1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="2" spans="1:84">
+    <row r="2" spans="1:110">
       <c r="A2">
         <v>1597830</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="E2">
         <v>24790890</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="I2">
         <v>355</v>
       </c>
       <c r="J2" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="U2" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="V2" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="AC2" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="AD2">
         <v>1</v>
@@ -1008,46 +1167,46 @@
         <v>3</v>
       </c>
       <c r="BC2" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="BD2">
         <v>12</v>
       </c>
       <c r="BE2" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="BF2">
         <v>352</v>
       </c>
       <c r="BG2" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="BH2">
         <v>7</v>
       </c>
       <c r="BI2" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="BJ2" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="BK2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="BL2">
         <v>24790890</v>
       </c>
       <c r="BM2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="BN2" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="BO2" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="BP2" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="BQ2">
         <v>11</v>
@@ -1056,39 +1215,42 @@
         <v>101</v>
       </c>
       <c r="BS2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="BT2">
         <v>1010</v>
       </c>
       <c r="BU2" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="BV2" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="BW2">
         <v>159950</v>
       </c>
       <c r="BX2" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="BY2" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="BZ2">
         <v>2026</v>
       </c>
       <c r="CC2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="CD2" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="CE2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CF2">
+        <v>135</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>136</v>
+      </c>
+      <c r="DF2">
         <v>1</v>
       </c>
     </row>
